--- a/data/trans_orig/Q03B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q03B_R-Edad-trans_orig.xlsx
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,02</t>
+          <t>0,76; 1,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,15</t>
+          <t>0,87; 1,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,4</t>
+          <t>1,14; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,23</t>
+          <t>1,86; 2,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,3</t>
+          <t>1,97; 2,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 2,35</t>
+          <t>2,05; 2,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,65</t>
+          <t>1,43; 1,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,83</t>
+          <t>1,62; 1,82</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,5</t>
+          <t>1,24; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,81</t>
+          <t>1,63; 1,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,47</t>
+          <t>3,13; 3,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 3,54</t>
+          <t>3,24; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,38</t>
+          <t>2,15; 2,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 2,65</t>
+          <t>2,43; 2,65</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,45</t>
+          <t>1,2; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,92</t>
+          <t>1,68; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 2,1</t>
+          <t>1,88; 2,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 4,37</t>
+          <t>4,02; 4,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 4,39</t>
+          <t>4,05; 4,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,05</t>
+          <t>3,74; 4,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 2,96</t>
+          <t>2,68; 2,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,16</t>
+          <t>2,89; 3,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,05</t>
+          <t>2,84; 3,06</t>
         </is>
       </c>
     </row>
@@ -1007,22 +1007,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,67</t>
+          <t>1,28; 1,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,66</t>
+          <t>1,43; 1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,02</t>
+          <t>1,74; 2,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 4,6</t>
+          <t>4,18; 4,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1032,22 +1032,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 4,1</t>
+          <t>3,81; 4,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,08</t>
+          <t>2,75; 3,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,04</t>
+          <t>2,77; 3,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,07</t>
+          <t>2,82; 3,07</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,63</t>
+          <t>1,16; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,27 +1127,27 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,84</t>
+          <t>1,54; 1,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 4,41</t>
+          <t>3,94; 4,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 4,35</t>
+          <t>3,92; 4,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 4,01</t>
+          <t>3,65; 4,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 2,98</t>
+          <t>2,63; 3,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 2,96</t>
+          <t>2,66; 2,93</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,39</t>
+          <t>1,03; 1,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,66</t>
+          <t>1,22; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,86</t>
+          <t>1,49; 1,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 3,73</t>
+          <t>3,28; 3,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 3,61</t>
+          <t>3,17; 3,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,92</t>
+          <t>3,49; 3,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 2,66</t>
+          <t>2,26; 2,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 2,65</t>
+          <t>2,31; 2,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 2,92</t>
+          <t>2,58; 2,9</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,31</t>
+          <t>0,91; 1,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,39</t>
+          <t>0,99; 1,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,36</t>
+          <t>1,08; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,17</t>
+          <t>2,54; 3,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,48</t>
+          <t>2,03; 2,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 2,83</t>
+          <t>2,41; 2,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,41</t>
+          <t>1,96; 2,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,0</t>
+          <t>1,68; 1,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,22</t>
+          <t>1,94; 2,23</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,2; 1,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,64</t>
+          <t>3,47; 3,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 3,54</t>
+          <t>3,39; 3,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,67</t>
+          <t>2,57; 2,66</t>
         </is>
       </c>
     </row>
